--- a/output/Data and Chart Outputs/vietnam_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/vietnam_power_generation_daily.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,6 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Vietnam power generation by source (EVN / NSMO daily; rooftop solar estimated) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -461,6 +463,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Vietnam peak demand (EVN / NSMO) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -969,7 +972,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -984,7 +986,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1059,7 +1060,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B2" t="n">
@@ -1085,7 +1086,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B3" t="n">
@@ -1111,7 +1112,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B4" t="n">
@@ -1137,7 +1138,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B5" t="n">
@@ -1163,7 +1164,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B6" t="n">
@@ -1189,7 +1190,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B7" t="n">
@@ -1215,7 +1216,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B8" t="n">
@@ -1241,7 +1242,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B9" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B10" t="n">
@@ -1293,7 +1294,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B11" t="n">
@@ -1319,7 +1320,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B12" t="n">
@@ -1345,7 +1346,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B13" t="n">
@@ -1371,7 +1372,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B14" t="n">
@@ -1397,7 +1398,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B15" t="n">
@@ -1423,7 +1424,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B16" t="n">
@@ -1449,7 +1450,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B17" t="n">
@@ -1475,7 +1476,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B18" t="n">
@@ -1501,7 +1502,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B19" t="n">
@@ -1527,7 +1528,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B20" t="n">
@@ -1553,7 +1554,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B21" t="n">
@@ -1579,7 +1580,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B22" t="n">
@@ -1605,7 +1606,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B23" t="n">
@@ -1631,7 +1632,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B24" t="n">
@@ -1657,7 +1658,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B25" t="n">
@@ -1683,7 +1684,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B26" t="n">
@@ -1709,7 +1710,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B27" t="n">
@@ -1735,7 +1736,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B28" t="n">
@@ -1761,7 +1762,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B29" t="n">
@@ -1787,7 +1788,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B30" t="n">
@@ -1813,7 +1814,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B31" t="n">
@@ -1839,7 +1840,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B32" t="n">
@@ -1865,7 +1866,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B33" t="n">
@@ -1891,7 +1892,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B34" t="n">
@@ -1917,7 +1918,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B35" t="n">
@@ -1943,7 +1944,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B36" t="n">
@@ -1969,7 +1970,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B37" t="n">
@@ -1995,7 +1996,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B38" t="n">
@@ -2021,7 +2022,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B39" t="n">
@@ -2047,7 +2048,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B40" t="n">
@@ -2073,7 +2074,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B41" t="n">
@@ -2129,7 +2130,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B2" t="n">
@@ -2137,7 +2138,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B3" t="n">
@@ -2145,7 +2146,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B4" t="n">
@@ -2153,7 +2154,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B5" t="n">
@@ -2161,7 +2162,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B6" t="n">
@@ -2169,7 +2170,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B7" t="n">
@@ -2177,7 +2178,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B8" t="n">
@@ -2185,7 +2186,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B9" t="n">
@@ -2193,7 +2194,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B10" t="n">
@@ -2201,7 +2202,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B11" t="n">
@@ -2209,7 +2210,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B12" t="n">
@@ -2217,7 +2218,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B13" t="n">
@@ -2225,7 +2226,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B14" t="n">
@@ -2233,7 +2234,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B15" t="n">
@@ -2241,7 +2242,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B16" t="n">
@@ -2249,7 +2250,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B17" t="n">
@@ -2257,7 +2258,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B18" t="n">
@@ -2265,7 +2266,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B19" t="n">
@@ -2273,7 +2274,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B20" t="n">
@@ -2281,7 +2282,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B21" t="n">
@@ -2289,7 +2290,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B22" t="n">
@@ -2297,7 +2298,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B23" t="n">
@@ -2305,7 +2306,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B24" t="n">
@@ -2313,7 +2314,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B25" t="n">
@@ -2321,7 +2322,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B26" t="n">
@@ -2329,7 +2330,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B27" t="n">
@@ -2337,7 +2338,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B28" t="n">
@@ -2345,7 +2346,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B29" t="n">
@@ -2353,7 +2354,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B30" t="n">
@@ -2361,7 +2362,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B31" t="n">
@@ -2369,7 +2370,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B32" t="n">
@@ -2377,7 +2378,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B33" t="n">
@@ -2385,7 +2386,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B34" t="n">
@@ -2393,7 +2394,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B35" t="n">
@@ -2401,7 +2402,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B36" t="n">
@@ -2409,7 +2410,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B37" t="n">
@@ -2417,7 +2418,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B38" t="n">
@@ -2425,7 +2426,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B39" t="n">
@@ -2433,7 +2434,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B40" t="n">
@@ -2441,7 +2442,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B41" t="n">
@@ -2449,7 +2450,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B42" t="n">
@@ -2457,7 +2458,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B43" t="n">

--- a/output/Data and Chart Outputs/vietnam_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/vietnam_power_generation_daily.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -160,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Vietnam power generation by source (EVN / NSMO daily; rooftop solar estimated) (to Sep/26)</a:t>
+              <a:t>Vietnam power generation by source (EVN / NSMO daily; rooftop solar estimated) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$41</f>
+              <f>'Chart'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$41</f>
+              <f>'Chart'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -246,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$41</f>
+              <f>'Chart'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -274,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$41</f>
+              <f>'Chart'!$E$2:$E$42</f>
             </numRef>
           </val>
         </ser>
@@ -302,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$41</f>
+              <f>'Chart'!$F$2:$F$42</f>
             </numRef>
           </val>
         </ser>
@@ -330,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$41</f>
+              <f>'Chart'!$G$2:$G$42</f>
             </numRef>
           </val>
         </ser>
@@ -358,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$41</f>
+              <f>'Chart'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$41</f>
+              <f>'Chart'!$H$2:$H$42</f>
             </numRef>
           </val>
         </ser>
@@ -968,10 +967,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Check: Total_MWh + Imports_MWh matches EVN's stated total within 1% on all but 1 days. A day whose figures repeat the next day's (a post filed under the wrong date) is dropped; where one source is clearly a typo (e.g. 20/9/2025 hydro '30,8' for 430,8) it is corrected to EVN's stated total: 2023-06-05: same figures as the next day (post filed under the wrong date) - dropped; 2024-08-23: same figures as the next day (post filed under the wrong date) - dropped; 2025-02-28: same figures as the next day (post filed under the wrong date) - dropped; 2025-07-04: same figures as the next day (post filed under the wrong date) - dropped; 2025-12-31: same figures as the next day (post filed under the wrong date) - dropped; 2026-01-30: same figures as the next day (post filed under the wrong date) - dropped; 2026-03-15: same figures as the next day (post filed under the wrong date) - dropped; 2023-06-04: a source is missing, so Total misses EVN's total - left for a re-read; 2023-08-01: Coal_MWh 408500 -&gt; 424200 MWh to match EVN's total; 2025-09-20: Hydro_MWh 30800 -&gt; 430800 MWh to match EVN's total.</t>
+          <t>Check: Total_MWh + Imports_MWh matches EVN's stated total within 1% on all but 1 days. A day whose figures repeat the next day's (a post filed under the wrong date) is dropped; where one source is clearly a typo (e.g. 20/9/2025 hydro '30,8' for 430,8) it is corrected to EVN's stated total: 2023-06-05: same figures as the next day (post filed under the wrong date) - dropped; 2023-06-04: a source is missing, so Total misses EVN's total - left for a re-read.</t>
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -982,10 +982,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily from 2023-05-28 to 2026-10-01 (1203 days; EVN posts the summary the next morning and skips the odd day). National power system (EVN / NSMO dispatch); rooftop solar is NSMO's estimate, not metered.</t>
+          <t>Daily from 2023-05-28 to 2026-10-26 (1228 days; EVN posts the summary the next morning and skips the odd day). National power system (EVN / NSMO dispatch); rooftop solar is NSMO's estimate, not metered.</t>
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1060,7 +1061,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B2" t="n">
@@ -1086,7 +1087,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B3" t="n">
@@ -1112,7 +1113,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B4" t="n">
@@ -1138,7 +1139,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B5" t="n">
@@ -1164,7 +1165,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B6" t="n">
@@ -1190,7 +1191,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B7" t="n">
@@ -1216,7 +1217,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B8" t="n">
@@ -1242,7 +1243,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B9" t="n">
@@ -1268,7 +1269,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B10" t="n">
@@ -1294,7 +1295,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B11" t="n">
@@ -1320,7 +1321,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B12" t="n">
@@ -1346,7 +1347,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B13" t="n">
@@ -1372,7 +1373,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B14" t="n">
@@ -1398,7 +1399,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B15" t="n">
@@ -1424,7 +1425,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B16" t="n">
@@ -1450,7 +1451,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B17" t="n">
@@ -1476,7 +1477,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B18" t="n">
@@ -1502,7 +1503,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B19" t="n">
@@ -1528,7 +1529,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B20" t="n">
@@ -1554,7 +1555,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B21" t="n">
@@ -1580,7 +1581,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B22" t="n">
@@ -1606,7 +1607,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B23" t="n">
@@ -1632,7 +1633,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B24" t="n">
@@ -1658,7 +1659,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B25" t="n">
@@ -1684,7 +1685,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B26" t="n">
@@ -1710,7 +1711,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B27" t="n">
@@ -1736,7 +1737,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B28" t="n">
@@ -1762,7 +1763,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B29" t="n">
@@ -1788,7 +1789,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B30" t="n">
@@ -1814,7 +1815,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B31" t="n">
@@ -1840,7 +1841,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B32" t="n">
@@ -1866,7 +1867,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B33" t="n">
@@ -1892,7 +1893,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B34" t="n">
@@ -1918,7 +1919,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B35" t="n">
@@ -1944,7 +1945,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B36" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B37" t="n">
@@ -1996,7 +1997,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B38" t="n">
@@ -2022,7 +2023,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B39" t="n">
@@ -2048,7 +2049,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B40" t="n">
@@ -2074,7 +2075,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B41" t="n">
@@ -2097,6 +2098,32 @@
       </c>
       <c r="H41" t="n">
         <v>99.19999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B42" t="n">
+        <v>6982.3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2263.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>918.1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2495.9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12713.4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2130,7 +2157,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B2" t="n">
@@ -2138,7 +2165,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B3" t="n">
@@ -2146,7 +2173,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B4" t="n">
@@ -2154,7 +2181,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B5" t="n">
@@ -2162,7 +2189,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B6" t="n">
@@ -2170,7 +2197,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B7" t="n">
@@ -2178,7 +2205,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B8" t="n">
@@ -2186,7 +2213,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B9" t="n">
@@ -2194,7 +2221,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B10" t="n">
@@ -2202,7 +2229,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B11" t="n">
@@ -2210,7 +2237,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B12" t="n">
@@ -2218,7 +2245,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B13" t="n">
@@ -2226,7 +2253,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B14" t="n">
@@ -2234,7 +2261,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B15" t="n">
@@ -2242,7 +2269,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B16" t="n">
@@ -2250,7 +2277,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B17" t="n">
@@ -2258,7 +2285,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B18" t="n">
@@ -2266,7 +2293,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B19" t="n">
@@ -2274,7 +2301,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B20" t="n">
@@ -2282,7 +2309,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B21" t="n">
@@ -2290,7 +2317,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B22" t="n">
@@ -2298,7 +2325,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B23" t="n">
@@ -2306,7 +2333,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B24" t="n">
@@ -2314,7 +2341,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B25" t="n">
@@ -2322,7 +2349,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B26" t="n">
@@ -2330,7 +2357,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B27" t="n">
@@ -2338,7 +2365,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B28" t="n">
@@ -2346,7 +2373,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B29" t="n">
@@ -2354,7 +2381,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B30" t="n">
@@ -2362,7 +2389,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B31" t="n">
@@ -2370,7 +2397,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B32" t="n">
@@ -2378,7 +2405,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B33" t="n">
@@ -2386,7 +2413,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B34" t="n">
@@ -2394,7 +2421,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B35" t="n">
@@ -2402,7 +2429,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B36" t="n">
@@ -2410,7 +2437,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B37" t="n">
@@ -2418,7 +2445,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B38" t="n">
@@ -2426,7 +2453,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B39" t="n">
@@ -2434,7 +2461,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B40" t="n">
@@ -2442,7 +2469,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B41" t="n">
@@ -2450,7 +2477,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B42" t="n">
@@ -2458,11 +2485,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B43" t="n">
-        <v>55034.1</v>
+        <v>50107.26923076923</v>
       </c>
     </row>
   </sheetData>
@@ -2477,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1204"/>
+  <dimension ref="A1:O1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53243,6 +53270,1106 @@
       </c>
       <c r="N1204" t="n">
         <v>1129700</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>359500</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>535100</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>83300</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>101000</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1205" t="n">
+        <v>1088400</v>
+      </c>
+      <c r="J1205" t="n">
+        <v>41900</v>
+      </c>
+      <c r="K1205" t="n">
+        <v>46100</v>
+      </c>
+      <c r="L1205" t="n">
+        <v>54900</v>
+      </c>
+      <c r="M1205" t="n">
+        <v>40800</v>
+      </c>
+      <c r="N1205" t="n">
+        <v>1130100</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>365200</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>508300</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>82400</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>100700</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1206" t="n">
+        <v>1063900</v>
+      </c>
+      <c r="J1206" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K1206" t="n">
+        <v>44400</v>
+      </c>
+      <c r="L1206" t="n">
+        <v>56300</v>
+      </c>
+      <c r="M1206" t="n">
+        <v>42800</v>
+      </c>
+      <c r="N1206" t="n">
+        <v>1103800</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>253800</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>485100</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>75900</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>7400</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>92500</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I1207" t="n">
+        <v>918100</v>
+      </c>
+      <c r="J1207" t="n">
+        <v>39800</v>
+      </c>
+      <c r="K1207" t="n">
+        <v>45300</v>
+      </c>
+      <c r="L1207" t="n">
+        <v>47200</v>
+      </c>
+      <c r="M1207" t="n">
+        <v>37700</v>
+      </c>
+      <c r="N1207" t="n">
+        <v>957600</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>246800</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>494100</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>69600</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>27300</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>101800</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1208" t="n">
+        <v>942900</v>
+      </c>
+      <c r="J1208" t="n">
+        <v>50300</v>
+      </c>
+      <c r="K1208" t="n">
+        <v>49600</v>
+      </c>
+      <c r="L1208" t="n">
+        <v>52200</v>
+      </c>
+      <c r="M1208" t="n">
+        <v>40400</v>
+      </c>
+      <c r="N1208" t="n">
+        <v>993100</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>239500</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>478400</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>92200</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>41400</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>85300</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I1209" t="n">
+        <v>940200</v>
+      </c>
+      <c r="J1209" t="n">
+        <v>56400</v>
+      </c>
+      <c r="K1209" t="n">
+        <v>39700</v>
+      </c>
+      <c r="L1209" t="n">
+        <v>45600</v>
+      </c>
+      <c r="M1209" t="n">
+        <v>33500</v>
+      </c>
+      <c r="N1209" t="n">
+        <v>996600</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>251300</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>463800</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>34800</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>91200</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>3700</v>
+      </c>
+      <c r="I1210" t="n">
+        <v>943800</v>
+      </c>
+      <c r="J1210" t="n">
+        <v>54000</v>
+      </c>
+      <c r="K1210" t="n">
+        <v>42700</v>
+      </c>
+      <c r="L1210" t="n">
+        <v>48500</v>
+      </c>
+      <c r="M1210" t="n">
+        <v>35700</v>
+      </c>
+      <c r="N1210" t="n">
+        <v>997800</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1211" t="n">
+        <v>246900</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>469300</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>90300</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>43500</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>86100</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1211" t="n">
+        <v>939600</v>
+      </c>
+      <c r="J1211" t="n">
+        <v>56700</v>
+      </c>
+      <c r="K1211" t="n">
+        <v>43000</v>
+      </c>
+      <c r="L1211" t="n">
+        <v>43100</v>
+      </c>
+      <c r="M1211" t="n">
+        <v>31100</v>
+      </c>
+      <c r="N1211" t="n">
+        <v>996200</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>258800</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>489700</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>77500</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>36200</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>84200</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I1212" t="n">
+        <v>950000</v>
+      </c>
+      <c r="J1212" t="n">
+        <v>55600</v>
+      </c>
+      <c r="K1212" t="n">
+        <v>38800</v>
+      </c>
+      <c r="L1212" t="n">
+        <v>45400</v>
+      </c>
+      <c r="M1212" t="n">
+        <v>33600</v>
+      </c>
+      <c r="N1212" t="n">
+        <v>1005500</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>233800</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>474000</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>68200</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>56800</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>80800</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I1213" t="n">
+        <v>917200</v>
+      </c>
+      <c r="J1213" t="n">
+        <v>64100</v>
+      </c>
+      <c r="K1213" t="n">
+        <v>41900</v>
+      </c>
+      <c r="L1213" t="n">
+        <v>38900</v>
+      </c>
+      <c r="M1213" t="n">
+        <v>28700</v>
+      </c>
+      <c r="N1213" t="n">
+        <v>981100</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1214" t="n">
+        <v>198400</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>424800</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>74100</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>48200</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>87000</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1214" t="n">
+        <v>836000</v>
+      </c>
+      <c r="J1214" t="n">
+        <v>57500</v>
+      </c>
+      <c r="K1214" t="n">
+        <v>42800</v>
+      </c>
+      <c r="L1214" t="n">
+        <v>44200</v>
+      </c>
+      <c r="M1214" t="n">
+        <v>32800</v>
+      </c>
+      <c r="N1214" t="n">
+        <v>893500</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>264600</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>459500</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>80200</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>40600</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>97200</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1215" t="n">
+        <v>945600</v>
+      </c>
+      <c r="J1215" t="n">
+        <v>56100</v>
+      </c>
+      <c r="K1215" t="n">
+        <v>48300</v>
+      </c>
+      <c r="L1215" t="n">
+        <v>48900</v>
+      </c>
+      <c r="M1215" t="n">
+        <v>34900</v>
+      </c>
+      <c r="N1215" t="n">
+        <v>1001600</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>274300</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>491900</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>77100</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>90700</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I1216" t="n">
+        <v>982100</v>
+      </c>
+      <c r="J1216" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K1216" t="n">
+        <v>43400</v>
+      </c>
+      <c r="L1216" t="n">
+        <v>47300</v>
+      </c>
+      <c r="M1216" t="n">
+        <v>33300</v>
+      </c>
+      <c r="N1216" t="n">
+        <v>1041900</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>260400</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>484600</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>83000</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>59500</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>104800</v>
+      </c>
+      <c r="H1217" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1217" t="n">
+        <v>995800</v>
+      </c>
+      <c r="J1217" t="n">
+        <v>62200</v>
+      </c>
+      <c r="K1217" t="n">
+        <v>49600</v>
+      </c>
+      <c r="L1217" t="n">
+        <v>55200</v>
+      </c>
+      <c r="M1217" t="n">
+        <v>40100</v>
+      </c>
+      <c r="N1217" t="n">
+        <v>1057900</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>292300</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>476100</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>93000</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>52500</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>85200</v>
+      </c>
+      <c r="H1218" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1218" t="n">
+        <v>1002600</v>
+      </c>
+      <c r="J1218" t="n">
+        <v>55000</v>
+      </c>
+      <c r="K1218" t="n">
+        <v>37100</v>
+      </c>
+      <c r="L1218" t="n">
+        <v>48100</v>
+      </c>
+      <c r="M1218" t="n">
+        <v>34100</v>
+      </c>
+      <c r="N1218" t="n">
+        <v>1057500</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>276000</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>473900</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>99200</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>50200</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>110200</v>
+      </c>
+      <c r="H1219" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I1219" t="n">
+        <v>1012900</v>
+      </c>
+      <c r="J1219" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K1219" t="n">
+        <v>51500</v>
+      </c>
+      <c r="L1219" t="n">
+        <v>58700</v>
+      </c>
+      <c r="M1219" t="n">
+        <v>43200</v>
+      </c>
+      <c r="N1219" t="n">
+        <v>1061900</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>271000</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>485700</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>103700</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>86600</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1220" t="n">
+        <v>996600</v>
+      </c>
+      <c r="J1220" t="n">
+        <v>47200</v>
+      </c>
+      <c r="K1220" t="n">
+        <v>38000</v>
+      </c>
+      <c r="L1220" t="n">
+        <v>48600</v>
+      </c>
+      <c r="M1220" t="n">
+        <v>34700</v>
+      </c>
+      <c r="N1220" t="n">
+        <v>1043800</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>199600</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>468400</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>80100</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>46800</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>80200</v>
+      </c>
+      <c r="H1221" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1221" t="n">
+        <v>878400</v>
+      </c>
+      <c r="J1221" t="n">
+        <v>53300</v>
+      </c>
+      <c r="K1221" t="n">
+        <v>40900</v>
+      </c>
+      <c r="L1221" t="n">
+        <v>39300</v>
+      </c>
+      <c r="M1221" t="n">
+        <v>28500</v>
+      </c>
+      <c r="N1221" t="n">
+        <v>931600</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>253000</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>498200</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>92700</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>46700</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1222" t="n">
+        <v>978900</v>
+      </c>
+      <c r="J1222" t="n">
+        <v>56800</v>
+      </c>
+      <c r="K1222" t="n">
+        <v>37800</v>
+      </c>
+      <c r="L1222" t="n">
+        <v>47200</v>
+      </c>
+      <c r="M1222" t="n">
+        <v>33900</v>
+      </c>
+      <c r="N1222" t="n">
+        <v>1035600</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1223" t="n">
+        <v>279300</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>499600</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>100800</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>100900</v>
+      </c>
+      <c r="H1223" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1223" t="n">
+        <v>1022200</v>
+      </c>
+      <c r="J1223" t="n">
+        <v>46700</v>
+      </c>
+      <c r="K1223" t="n">
+        <v>47500</v>
+      </c>
+      <c r="L1223" t="n">
+        <v>53400</v>
+      </c>
+      <c r="M1223" t="n">
+        <v>39100</v>
+      </c>
+      <c r="N1223" t="n">
+        <v>1068700</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>276200</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>499600</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>95800</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>102500</v>
+      </c>
+      <c r="H1224" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1224" t="n">
+        <v>1017000</v>
+      </c>
+      <c r="J1224" t="n">
+        <v>50900</v>
+      </c>
+      <c r="K1224" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L1224" t="n">
+        <v>52500</v>
+      </c>
+      <c r="M1224" t="n">
+        <v>38600</v>
+      </c>
+      <c r="N1224" t="n">
+        <v>1067700</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1225" t="n">
+        <v>272200</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>513400</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>93800</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>40800</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>102300</v>
+      </c>
+      <c r="H1225" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1225" t="n">
+        <v>1029400</v>
+      </c>
+      <c r="J1225" t="n">
+        <v>46100</v>
+      </c>
+      <c r="K1225" t="n">
+        <v>49900</v>
+      </c>
+      <c r="L1225" t="n">
+        <v>52400</v>
+      </c>
+      <c r="M1225" t="n">
+        <v>38600</v>
+      </c>
+      <c r="N1225" t="n">
+        <v>1075300</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1226" t="n">
+        <v>300600</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>513600</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>97100</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>5900</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>18600</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>110000</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1226" t="n">
+        <v>1049100</v>
+      </c>
+      <c r="J1226" t="n">
+        <v>29400</v>
+      </c>
+      <c r="K1226" t="n">
+        <v>54600</v>
+      </c>
+      <c r="L1226" t="n">
+        <v>55400</v>
+      </c>
+      <c r="M1226" t="n">
+        <v>41200</v>
+      </c>
+      <c r="N1226" t="n">
+        <v>1078400</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>283000</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>524100</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>98700</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>108700</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1227" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="J1227" t="n">
+        <v>30800</v>
+      </c>
+      <c r="K1227" t="n">
+        <v>55900</v>
+      </c>
+      <c r="L1227" t="n">
+        <v>52800</v>
+      </c>
+      <c r="M1227" t="n">
+        <v>39000</v>
+      </c>
+      <c r="N1227" t="n">
+        <v>1060600</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1228" t="n">
+        <v>221200</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>484400</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>90400</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>21300</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>96100</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I1228" t="n">
+        <v>916600</v>
+      </c>
+      <c r="J1228" t="n">
+        <v>38800</v>
+      </c>
+      <c r="K1228" t="n">
+        <v>51800</v>
+      </c>
+      <c r="L1228" t="n">
+        <v>44300</v>
+      </c>
+      <c r="M1228" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N1228" t="n">
+        <v>955300</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>236500</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>495400</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>58600</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>112500</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I1229" t="n">
+        <v>998300</v>
+      </c>
+      <c r="J1229" t="n">
+        <v>53500</v>
+      </c>
+      <c r="K1229" t="n">
+        <v>56200</v>
+      </c>
+      <c r="L1229" t="n">
+        <v>56300</v>
+      </c>
+      <c r="M1229" t="n">
+        <v>41400</v>
+      </c>
+      <c r="N1229" t="n">
+        <v>1051800</v>
       </c>
     </row>
   </sheetData>
@@ -53256,7 +54383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1204"/>
+  <dimension ref="A1:D1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67937,6 +69064,356 @@
       </c>
       <c r="D1204" t="n">
         <v>49855.6</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>55240.6</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>49954.9</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>49280.1</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>53938.8</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>48809.1</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>46858.3</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>43204.2</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>39694.6</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>40396.7</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>49848.1</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>43514</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>43341.4</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>49481.3</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>41725.3</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>42650.6</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>49203.8</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>42826</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>42600.2</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1211" t="n">
+        <v>49356.8</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>42477</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>42239.1</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>49314.1</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>42463.2</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>43493.1</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>47618.8</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>40352.1</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>41435.1</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1214" t="n">
+        <v>43565.3</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>35917.2</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>39275.7</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>50294.2</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>44012</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>44346.7</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>51147.1</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>44719.6</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>44939.9</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>51431</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>45840.5</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>46150.7</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>50849.6</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>45444</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>45073.4</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>52059.5</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>46340.7</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>45949.5</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>50913.1</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>45185</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>43954.4</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>43412.9</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>38371.4</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>40769.4</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>51057.7</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>46018.9</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>45733.8</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1223" t="n">
+        <v>52394.7</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>46653</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>45699.9</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>52169.1</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>46432</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>46142.1</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1225" t="n">
+        <v>52174.3</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>46854.7</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>46121.5</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1226" t="n">
+        <v>52428.4</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>47102.5</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>46129.6</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>50892.3</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>46483.2</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>45301.4</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1228" t="n">
+        <v>44164.8</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>38599.5</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>42183.3</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>51594.4</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>46259.9</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>46343.5</v>
       </c>
     </row>
   </sheetData>
